--- a/Design/Project WBS and Criteria.xlsx
+++ b/Design/Project WBS and Criteria.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="212" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2DF9521F-2648-4398-933E-FD9A047AC27C}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Adam\Documents\GitHub\Vanadam Website\design\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5657E367-25AA-481B-B1C0-1F34F7381F6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Asessment Criteria" sheetId="2" r:id="rId1"/>
@@ -492,7 +497,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1062,13 +1067,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73C69F01-1180-44B1-9BFC-13F7580039DD}">
   <dimension ref="A1:C34"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="120.140625" customWidth="1"/>
     <col min="3" max="3" width="29.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.75">
+    <row r="1" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1079,7 +1084,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -1088,7 +1093,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
@@ -1097,7 +1102,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
@@ -1106,7 +1111,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -1115,7 +1120,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>11</v>
       </c>
@@ -1124,17 +1129,17 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>15</v>
       </c>
@@ -1143,7 +1148,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>17</v>
       </c>
@@ -1152,7 +1157,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>19</v>
       </c>
@@ -1161,7 +1166,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>20</v>
       </c>
@@ -1170,7 +1175,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>22</v>
       </c>
@@ -1179,7 +1184,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>24</v>
       </c>
@@ -1188,17 +1193,17 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="18.75">
+    <row r="15" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="18.75">
+    <row r="16" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>28</v>
       </c>
@@ -1207,7 +1212,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>30</v>
       </c>
@@ -1216,7 +1221,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>32</v>
       </c>
@@ -1225,7 +1230,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>34</v>
       </c>
@@ -1234,7 +1239,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>36</v>
       </c>
@@ -1243,7 +1248,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="30.75">
+    <row r="22" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>38</v>
       </c>
@@ -1252,7 +1257,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>40</v>
       </c>
@@ -1261,17 +1266,17 @@
         <v>41</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="18.75">
+    <row r="24" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="18.75">
+    <row r="25" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>43</v>
       </c>
@@ -1280,7 +1285,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>45</v>
       </c>
@@ -1289,7 +1294,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>47</v>
       </c>
@@ -1298,13 +1303,13 @@
         <v>37</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>48</v>
       </c>
       <c r="B29" s="7"/>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>49</v>
       </c>
@@ -1313,7 +1318,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>50</v>
       </c>
@@ -1322,17 +1327,17 @@
         <v>51</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="18.75">
+    <row r="32" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="33" spans="1:1" ht="18.75">
+    <row r="33" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>53</v>
       </c>
@@ -1345,12 +1350,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59D453F1-F8D2-4DCD-8751-C9A01C923A6C}">
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="124.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="8">
         <v>1</v>
       </c>
@@ -1358,7 +1363,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
         <v>55</v>
       </c>
@@ -1366,7 +1371,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>57</v>
       </c>
@@ -1374,7 +1379,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>59</v>
       </c>
@@ -1382,7 +1387,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
         <v>61</v>
       </c>
@@ -1390,7 +1395,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>63</v>
       </c>
@@ -1398,7 +1403,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>65</v>
       </c>
@@ -1406,7 +1411,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
         <v>2</v>
       </c>
@@ -1414,7 +1419,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
         <v>55</v>
       </c>
@@ -1422,7 +1427,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>59</v>
       </c>
@@ -1430,7 +1435,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
         <v>61</v>
       </c>
@@ -1438,7 +1443,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>71</v>
       </c>
@@ -1446,7 +1451,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
         <v>57</v>
       </c>
@@ -1454,7 +1459,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
         <v>63</v>
       </c>
@@ -1462,7 +1467,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
         <v>65</v>
       </c>
@@ -1470,7 +1475,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="12">
         <v>3</v>
       </c>
@@ -1486,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I19"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
     <col min="5" max="5" width="22.5703125" bestFit="1" customWidth="1"/>
@@ -1496,7 +1501,7 @@
     <col min="9" max="9" width="14.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>77</v>
       </c>
@@ -1525,7 +1530,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>86</v>
       </c>
@@ -1545,7 +1550,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>31</v>
       </c>
@@ -1565,7 +1570,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>89</v>
       </c>
@@ -1579,7 +1584,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>92</v>
       </c>
@@ -1599,7 +1604,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>96</v>
       </c>
@@ -1613,7 +1618,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>98</v>
       </c>
@@ -1627,7 +1632,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>101</v>
       </c>
@@ -1641,7 +1646,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>103</v>
       </c>
@@ -1655,7 +1660,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>105</v>
       </c>
@@ -1675,7 +1680,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>107</v>
       </c>
@@ -1692,7 +1697,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>111</v>
       </c>
@@ -1709,7 +1714,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>113</v>
       </c>
@@ -1726,7 +1731,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>116</v>
       </c>
@@ -1743,7 +1748,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>119</v>
       </c>
@@ -1760,7 +1765,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>118</v>
       </c>
@@ -1768,7 +1773,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>121</v>
       </c>
@@ -1776,7 +1781,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>110</v>
       </c>
@@ -1784,7 +1789,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>94</v>
       </c>
@@ -1797,14 +1802,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{762D7B69-3157-4B93-AED2-94748130EDD9}">
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>122</v>
       </c>
@@ -1818,7 +1823,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>126</v>
       </c>
@@ -1826,7 +1831,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>128</v>
       </c>
@@ -1834,7 +1839,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>129</v>
       </c>
@@ -1845,7 +1850,7 @@
         <v>45758</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>130</v>
       </c>
@@ -1856,7 +1861,7 @@
         <v>45758</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>131</v>
       </c>
